--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41EFBC2-8727-4C83-AA14-42836877D22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3B682B-7E16-498D-AB3D-8FC7DB51D445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="317">
   <si>
     <t>P0-01</t>
   </si>
@@ -976,6 +976,9 @@
   </si>
   <si>
     <t>已完成</t>
+  </si>
+  <si>
+    <t>进行中</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>79</v>
@@ -1694,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>82</v>
@@ -1738,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>72</v>
+        <v>316</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>88</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3B682B-7E16-498D-AB3D-8FC7DB51D445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB91A121-02C0-4798-AAE9-3351A701D320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8930" yWindow="-21690" windowWidth="38580" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="316">
   <si>
     <t>P0-01</t>
   </si>
@@ -976,9 +976,6 @@
   </si>
   <si>
     <t>已完成</t>
-  </si>
-  <si>
-    <t>进行中</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>88</v>
@@ -1763,7 +1760,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>92</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB91A121-02C0-4798-AAE9-3351A701D320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CE0675-B3B1-42C2-8991-64A010787DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8930" yWindow="-21690" windowWidth="38580" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1786,7 +1786,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>17</v>
@@ -1808,7 +1808,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CE0675-B3B1-42C2-8991-64A010787DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB0ECB5-2CFE-4042-80B4-D007E2EDEE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8930" yWindow="-21690" windowWidth="38580" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1830,7 +1830,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>99</v>
@@ -1852,7 +1852,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>102</v>
@@ -1874,7 +1874,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>105</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB0ECB5-2CFE-4042-80B4-D007E2EDEE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D1F132-9AB4-408C-8394-4B7AEBDE4459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ACEE59-C05F-47BE-ABCD-7BF9C79A4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3D628-A197-4CD2-931C-B370CD80781F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="317">
   <si>
     <t>P0-01</t>
   </si>
@@ -970,6 +970,9 @@
   </si>
   <si>
     <t>已完成</t>
+  </si>
+  <si>
+    <t>进行中</t>
   </si>
   <si>
     <t>测试常见 RTSP 地址</t>
@@ -1946,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>71</v>
+        <v>313</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>113</v>
@@ -1962,13 +1965,13 @@
         <v>28</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>71</v>
+        <v>314</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>115</v>
@@ -2006,7 +2009,7 @@
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3D628-A197-4CD2-931C-B370CD80781F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89264563-6CFE-44FB-B333-392D5A2CD3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="332">
   <si>
     <t>P0-01</t>
   </si>
@@ -150,9 +150,6 @@
     <t>P3-06</t>
   </si>
   <si>
-    <t>interrupt boot</t>
-  </si>
-  <si>
     <t>P4-01</t>
   </si>
   <si>
@@ -168,9 +165,6 @@
     <t>P4-05</t>
   </si>
   <si>
-    <t>UART login</t>
-  </si>
-  <si>
     <t>P4-06</t>
   </si>
   <si>
@@ -435,96 +429,33 @@
     <t>断电状态下确认 GND 引脚</t>
   </si>
   <si>
-    <t>万用表</t>
-  </si>
-  <si>
-    <t>GND 与大面积铜皮导通</t>
-  </si>
-  <si>
-    <t>测量 RX / TX 空闲电平</t>
-  </si>
-  <si>
-    <t>确认是 3.3 V TTL，禁止 5 V</t>
-  </si>
-  <si>
-    <t>只连接摄像头 TX 到 USB-TTL RX</t>
-  </si>
-  <si>
     <t>USB-TTL / 杜邦线</t>
   </si>
   <si>
-    <t>能安全读取输出，不向摄像头写入</t>
-  </si>
-  <si>
-    <t>尝试读取 boot log</t>
-  </si>
-  <si>
-    <t>PuTTY / MobaXterm / minicom</t>
-  </si>
-  <si>
-    <t>能看到启动日志</t>
-  </si>
-  <si>
-    <t>尝试不同波特率</t>
-  </si>
-  <si>
     <t>115200 / 57600 / 38400 / 9600</t>
   </si>
   <si>
-    <t>找到正确串口参数</t>
-  </si>
-  <si>
-    <t>保存完整 boot log</t>
-  </si>
-  <si>
     <t>UART log</t>
   </si>
   <si>
-    <t>保存启动日志文本</t>
-  </si>
-  <si>
     <t>P3-07</t>
   </si>
   <si>
-    <t>从 boot log 识别系统信息</t>
-  </si>
-  <si>
     <t>Linux boot log</t>
   </si>
   <si>
-    <t>获得 kernel、rootfs、mtd 分区、启动参数</t>
-  </si>
-  <si>
     <t>P3-08</t>
   </si>
   <si>
-    <t>再连接 USB-TTL TX 到摄像头 RX</t>
-  </si>
-  <si>
     <t>USB-TTL</t>
   </si>
   <si>
-    <t>可以向设备输入字符</t>
-  </si>
-  <si>
     <t>P3-09</t>
   </si>
   <si>
-    <t>判断是否可登录 shell</t>
-  </si>
-  <si>
-    <t>判断是否有 login / shell / root 权限</t>
-  </si>
-  <si>
     <t>P3-10</t>
   </si>
   <si>
-    <t>判断是否可中断 U-Boot</t>
-  </si>
-  <si>
-    <t>判断是否可进入 bootloader 命令行</t>
-  </si>
-  <si>
     <t>固件备份与恢复</t>
   </si>
   <si>
@@ -970,9 +901,6 @@
   </si>
   <si>
     <t>已完成</t>
-  </si>
-  <si>
-    <t>进行中</t>
   </si>
   <si>
     <t>测试常见 RTSP 地址</t>
@@ -980,6 +908,130 @@
   </si>
   <si>
     <t>尝试 HTTP / MJPEG / 私有流地址,加入 8800/tcp 私有协议探测。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳过此步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首先读UART</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳过</t>
+  </si>
+  <si>
+    <t>上电后测量 RX / TX 空闲电平</t>
+  </si>
+  <si>
+    <t>制定并确认只读接线方案</t>
+  </si>
+  <si>
+    <t>只读接线并打开串口日志保存</t>
+  </si>
+  <si>
+    <t>上电读取 boot log 并观察输出</t>
+  </si>
+  <si>
+    <t>尝试不同波特率但保持只读</t>
+  </si>
+  <si>
+    <t>保存完整只读 boot log</t>
+  </si>
+  <si>
+    <t>P3-05 / P3-06</t>
+  </si>
+  <si>
+    <t>从 boot log 识别系统和服务信息</t>
+  </si>
+  <si>
+    <t>分析 8800 / 9800 端口归属线索</t>
+  </si>
+  <si>
+    <t>评估是否需要进入交互式 UART</t>
+  </si>
+  <si>
+    <t>P3-11</t>
+  </si>
+  <si>
+    <t>如获批准再连接 USB-TTL TX 并测试只输入回车</t>
+  </si>
+  <si>
+    <t>P3-12</t>
+  </si>
+  <si>
+    <t>如获批准再评估是否可中断 U-Boot</t>
+  </si>
+  <si>
+    <t>万用表蜂鸣档</t>
+  </si>
+  <si>
+    <t>GND 与大面积铜皮导通；拍照记录测试点</t>
+  </si>
+  <si>
+    <t>万用表直流电压档</t>
+  </si>
+  <si>
+    <t>确认 UART 为 3.3 V TTL；若出现 5 V 则停止</t>
+  </si>
+  <si>
+    <t>仅允许摄像头 GND 接 USB-TTL GND；摄像头 TX 接 USB-TTL RX；暂不连接 USB-TTL TX</t>
+  </si>
+  <si>
+    <t>PuTTY / MobaXterm / Tera Term</t>
+  </si>
+  <si>
+    <t>串口工具已设置日志保存；初始参数 115200 8N1</t>
+  </si>
+  <si>
+    <t>记录正常日志 / 乱码 / 无输出 / login 提示 / U-Boot 倒计时等现象</t>
+  </si>
+  <si>
+    <t>在不输入字符的前提下找到可读串口参数</t>
+  </si>
+  <si>
+    <t>保存从上电到启动完成的完整日志文本</t>
+  </si>
+  <si>
+    <t>获得 kernel、rootfs、mtd 分区、启动参数、进程和服务线索</t>
+  </si>
+  <si>
+    <t>boot log / service names</t>
+  </si>
+  <si>
+    <t>判断私有端口可能对应的进程或启动脚本</t>
+  </si>
+  <si>
+    <t>只有在明确收益和风险后才考虑连接 USB-TTL TX 到摄像头 RX</t>
+  </si>
+  <si>
+    <t>验证是否存在 login / shell；不输入破坏性命令</t>
+  </si>
+  <si>
+    <t>bootloader console</t>
+  </si>
+  <si>
+    <t>仅评估是否存在倒计时和交互入口；默认不中断启动</t>
+  </si>
+  <si>
+    <t>P3-08</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1020,7 +1072,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1237,11 +1289,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1289,11 +1350,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1319,6 +1386,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1598,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EC9ED9-E219-4173-AB5E-59042C60AAEE}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -1608,11 +1682,11 @@
     <col min="5" max="5" width="15.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="84.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1632,13 +1706,16 @@
         <v>8</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>12</v>
       </c>
@@ -1649,132 +1726,132 @@
         <v>0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="15"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="15"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="15"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="15"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1785,136 +1862,136 @@
         <v>16</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="15"/>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="15"/>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="15"/>
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="15"/>
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="16"/>
       <c r="C14" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>24</v>
@@ -1923,21 +2000,24 @@
         <v>21</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>26</v>
@@ -1949,104 +2029,116 @@
         <v>16</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="15"/>
       <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="15"/>
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="15"/>
       <c r="C18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="15"/>
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="H19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="15"/>
       <c r="C20" s="1" t="s">
@@ -2059,1216 +2151,1266 @@
         <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="16"/>
       <c r="C21" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>71</v>
+        <v>299</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="B22" s="14" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="15"/>
       <c r="C23" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>137</v>
+        <v>300</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>135</v>
+        <v>316</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="15"/>
       <c r="C24" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>139</v>
+        <v>301</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="15"/>
       <c r="C25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>142</v>
+        <v>302</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>143</v>
+        <v>319</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="15"/>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="15"/>
       <c r="C27" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>148</v>
+        <v>304</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="15"/>
       <c r="C28" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>152</v>
+        <v>305</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>39</v>
+        <v>306</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="15"/>
       <c r="C29" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>156</v>
+        <v>307</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="15"/>
       <c r="C30" s="1" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>46</v>
+        <v>325</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>174</v>
+      <c r="D34" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="15"/>
       <c r="C35" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="15"/>
       <c r="C36" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="15"/>
       <c r="C37" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="15"/>
       <c r="C38" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="15"/>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="15"/>
       <c r="C40" s="1" t="s">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="15"/>
       <c r="C41" s="1" t="s">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="15"/>
       <c r="C42" s="1" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>205</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>212</v>
+      <c r="A44" s="12"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>215</v>
+      <c r="A46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="15"/>
       <c r="C47" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="15"/>
       <c r="C48" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="15"/>
       <c r="C49" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>190</v>
+        <v>51</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="15"/>
       <c r="C50" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="15"/>
       <c r="C51" s="1" t="s">
-        <v>228</v>
+        <v>56</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>236</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="E53" s="5" t="s">
+      <c r="D55" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>246</v>
+      <c r="F55" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="15"/>
       <c r="C56" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="15"/>
       <c r="C57" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>56</v>
+        <v>222</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="15"/>
       <c r="C58" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>65</v>
+        <v>225</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="15"/>
       <c r="C59" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>257</v>
+        <v>54</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="15"/>
       <c r="C60" s="1" t="s">
-        <v>259</v>
+        <v>67</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="15"/>
       <c r="C61" s="1" t="s">
-        <v>263</v>
+        <v>68</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>265</v>
+        <v>67</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>271</v>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="12"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>280</v>
+      <c r="A63" s="12"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="13"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>284</v>
+      <c r="A65" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="12"/>
       <c r="B66" s="15"/>
       <c r="C66" s="1" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="15"/>
       <c r="C67" s="1" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>66</v>
+        <v>260</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="15"/>
       <c r="C68" s="1" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="15"/>
       <c r="C69" s="1" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>299</v>
+        <v>64</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="15"/>
       <c r="C70" s="1" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="15"/>
       <c r="C71" s="1" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>68</v>
+        <v>276</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>312</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="12"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="12"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="13"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="A63:A72"/>
+    <mergeCell ref="A55:A64"/>
+    <mergeCell ref="A65:A74"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="B8:B14"/>
     <mergeCell ref="B15:B21"/>
-    <mergeCell ref="B22:B31"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="B44:B52"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="B63:B72"/>
+    <mergeCell ref="B22:B33"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="B46:B54"/>
+    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B65:B74"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A14"/>
     <mergeCell ref="A15:A21"/>
-    <mergeCell ref="A22:A31"/>
-    <mergeCell ref="A32:A43"/>
-    <mergeCell ref="A44:A52"/>
+    <mergeCell ref="A22:A33"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="A46:A54"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F2:F72">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="F2:F74">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"跳过"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"失败"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"已完成"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"进行中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"待处理"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F72" xr:uid="{6104A060-77CA-469A-B9D5-832314748402}">
-      <formula1>"待处理,进行中,已完成,失败"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74" xr:uid="{6104A060-77CA-469A-B9D5-832314748402}">
+      <formula1>"待处理,进行中,已完成,失败,跳过"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89264563-6CFE-44FB-B333-392D5A2CD3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26A4702-051E-48B9-90B5-CC9A7474BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="327">
   <si>
     <t>P0-01</t>
   </si>
@@ -911,30 +911,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不支持</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跳过此步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>首先读UART</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>跳过</t>
   </si>
   <si>
@@ -960,9 +936,6 @@
   </si>
   <si>
     <t>从 boot log 识别系统和服务信息</t>
-  </si>
-  <si>
-    <t>分析 8800 / 9800 端口归属线索</t>
   </si>
   <si>
     <t>评估是否需要进入交互式 UART</t>
@@ -1033,6 +1006,13 @@
   <si>
     <t>P3-08</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进行中</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1052,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1289,20 +1269,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1349,12 +1320,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1672,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EC9ED9-E219-4173-AB5E-59042C60AAEE}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -1683,10 +1648,9 @@
     <col min="6" max="6" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.88671875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="84.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1711,11 +1675,8 @@
       <c r="H1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>12</v>
       </c>
@@ -1741,7 +1702,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="15"/>
       <c r="C3" s="1" t="s">
@@ -1763,7 +1724,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="15"/>
       <c r="C4" s="1" t="s">
@@ -1785,7 +1746,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="15"/>
       <c r="C5" s="1" t="s">
@@ -1807,7 +1768,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="15"/>
       <c r="C6" s="1" t="s">
@@ -1829,7 +1790,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
@@ -1851,7 +1812,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1877,7 +1838,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="15"/>
       <c r="C9" s="1" t="s">
@@ -1899,7 +1860,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="15"/>
       <c r="C10" s="1" t="s">
@@ -1921,7 +1882,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="15"/>
       <c r="C11" s="1" t="s">
@@ -1943,7 +1904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="15"/>
       <c r="C12" s="1" t="s">
@@ -1965,7 +1926,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="C13" s="1" t="s">
@@ -1987,7 +1948,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="16"/>
       <c r="C14" s="8" t="s">
@@ -2008,11 +1969,8 @@
       <c r="H14" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="I14" s="18" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2038,7 +1996,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="15"/>
       <c r="C16" s="1" t="s">
@@ -2059,11 +2017,8 @@
       <c r="H16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="18" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="15"/>
       <c r="C17" s="1" t="s">
@@ -2084,11 +2039,8 @@
       <c r="H17" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="18" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="15"/>
       <c r="C18" s="1" t="s">
@@ -2109,11 +2061,8 @@
       <c r="H18" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="15"/>
       <c r="C19" s="1" t="s">
@@ -2126,7 +2075,7 @@
         <v>121</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>122</v>
@@ -2134,11 +2083,8 @@
       <c r="H19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="18" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="15"/>
       <c r="C20" s="1" t="s">
@@ -2159,11 +2105,8 @@
       <c r="H20" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="16"/>
       <c r="C21" s="8" t="s">
@@ -2176,7 +2119,7 @@
         <v>33</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>128</v>
@@ -2185,7 +2128,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>130</v>
       </c>
@@ -2202,23 +2145,23 @@
         <v>33</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>69</v>
+        <v>326</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="15"/>
       <c r="C23" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
@@ -2227,20 +2170,20 @@
         <v>69</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="15"/>
       <c r="C24" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>35</v>
@@ -2252,17 +2195,17 @@
         <v>133</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="15"/>
       <c r="C25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>36</v>
@@ -2271,20 +2214,20 @@
         <v>69</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="15"/>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>37</v>
@@ -2296,17 +2239,17 @@
         <v>135</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="15"/>
       <c r="C27" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>38</v>
@@ -2318,20 +2261,20 @@
         <v>134</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="15"/>
       <c r="C28" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>69</v>
@@ -2340,17 +2283,17 @@
         <v>135</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="15"/>
       <c r="C29" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>136</v>
@@ -2362,17 +2305,17 @@
         <v>137</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="15"/>
       <c r="C30" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>138</v>
@@ -2381,20 +2324,20 @@
         <v>69</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="15"/>
       <c r="C31" s="1" t="s">
         <v>141</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>138</v>
@@ -2406,17 +2349,17 @@
         <v>128</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="15"/>
       <c r="C32" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>141</v>
@@ -2428,17 +2371,17 @@
         <v>139</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="16"/>
       <c r="C33" s="8" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>141</v>
@@ -2447,10 +2390,10 @@
         <v>69</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -2467,7 +2410,7 @@
         <v>143</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>69</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26A4702-051E-48B9-90B5-CC9A7474BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328623E0-B900-4F1E-A0DD-E35D22F5BB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2145,7 +2145,7 @@
         <v>33</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>307</v>
@@ -2167,7 +2167,7 @@
         <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>309</v>
@@ -2189,7 +2189,7 @@
         <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>133</v>
@@ -2211,7 +2211,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>312</v>
@@ -2233,7 +2233,7 @@
         <v>37</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>135</v>
@@ -2255,7 +2255,7 @@
         <v>38</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>134</v>
@@ -2277,7 +2277,7 @@
         <v>300</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>69</v>
+        <v>290</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>135</v>
@@ -2299,7 +2299,7 @@
         <v>136</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>69</v>
+        <v>326</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>137</v>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328623E0-B900-4F1E-A0DD-E35D22F5BB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34DDB18-8FD8-46EB-BCA9-E30C1400861C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28130" yWindow="-21600" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="330">
   <si>
     <t>P0-01</t>
   </si>
@@ -1008,11 +1008,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进行中</t>
+    <t>分析 8800 / 9800 端口归属线索</t>
+  </si>
+  <si>
+    <t>P3-13</t>
+  </si>
+  <si>
+    <t>同步抓取 UART 与 pcap 并关联 App 预览/PTZ/断连现象</t>
+  </si>
+  <si>
+    <t>UART log / Wireshark pcapng</t>
+  </si>
+  <si>
+    <t>确认断连对应摄像头侧 WiFi 重连与 P2P 重新登录；未见手机直连或 8800/9800 流量</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1060,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1269,11 +1277,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1320,6 +1354,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1637,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EC9ED9-E219-4173-AB5E-59042C60AAEE}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -2299,7 +2342,7 @@
         <v>136</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>137</v>
@@ -2314,7 +2357,7 @@
       <c r="C30" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="17" t="s">
         <v>325</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2374,150 +2417,150 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="8" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="F33" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="19" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+    <row r="34" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B35" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="F35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="15"/>
       <c r="C36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="15"/>
       <c r="C37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="15"/>
       <c r="C38" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="15"/>
       <c r="C39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>43</v>
@@ -2526,64 +2569,64 @@
         <v>69</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="15"/>
       <c r="C40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="15"/>
       <c r="C41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="15"/>
       <c r="C42" s="1" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>46</v>
@@ -2592,134 +2635,134 @@
         <v>69</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="15"/>
       <c r="C43" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="15"/>
       <c r="C44" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="F45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H45" s="7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="8" t="s">
+    <row r="46" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D46" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E46" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G45" s="8" t="s">
+      <c r="F46" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H46" s="9" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B47" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="F47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="15"/>
       <c r="C48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>50</v>
@@ -2728,86 +2771,86 @@
         <v>69</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="15"/>
       <c r="C49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="15"/>
       <c r="C50" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="15"/>
       <c r="C51" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="15"/>
       <c r="C52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>167</v>
@@ -2816,178 +2859,178 @@
         <v>69</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="15"/>
       <c r="C53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="12"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="F54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H54" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="8" t="s">
+    <row r="55" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="F54" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G54" s="8" t="s">
+      <c r="F55" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B56" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="F56" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="15"/>
       <c r="C57" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="15"/>
       <c r="C58" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="15"/>
       <c r="C59" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="15"/>
       <c r="C60" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>63</v>
@@ -2996,244 +3039,244 @@
         <v>69</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>231</v>
+        <v>54</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="15"/>
       <c r="C61" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
       <c r="B62" s="15"/>
       <c r="C62" s="1" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="15"/>
       <c r="C63" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="F64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H64" s="7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="8" t="s">
+    <row r="65" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="13"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D65" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E65" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G64" s="8" t="s">
+      <c r="F65" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G65" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H65" s="9" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B66" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="F66" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H65" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="15"/>
       <c r="C67" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="15"/>
       <c r="C68" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="15"/>
       <c r="C69" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="15"/>
       <c r="C70" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>267</v>
+        <v>62</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="15"/>
       <c r="C71" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>267</v>
@@ -3242,99 +3285,121 @@
         <v>69</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="15"/>
       <c r="C72" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>65</v>
+        <v>267</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="15"/>
       <c r="C73" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="12"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="F74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H73" s="7" t="s">
+      <c r="H74" s="7" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="8" t="s">
+    <row r="75" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="13"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D75" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E75" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="F74" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G74" s="8" t="s">
+      <c r="F75" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="H74" s="9" t="s">
+      <c r="H75" s="9" t="s">
         <v>289</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A55:A64"/>
-    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="A56:A65"/>
+    <mergeCell ref="A66:A75"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="B8:B14"/>
     <mergeCell ref="B15:B21"/>
-    <mergeCell ref="B22:B33"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="B46:B54"/>
-    <mergeCell ref="B55:B64"/>
-    <mergeCell ref="B65:B74"/>
+    <mergeCell ref="B22:B34"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="B47:B55"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="B66:B75"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A14"/>
     <mergeCell ref="A15:A21"/>
-    <mergeCell ref="A22:A33"/>
-    <mergeCell ref="A34:A45"/>
-    <mergeCell ref="A46:A54"/>
+    <mergeCell ref="A22:A34"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A47:A55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F2:F74">
+  <conditionalFormatting sqref="F2:F75">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"跳过"</formula>
     </cfRule>
@@ -3352,7 +3417,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F74" xr:uid="{6104A060-77CA-469A-B9D5-832314748402}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F75" xr:uid="{6104A060-77CA-469A-B9D5-832314748402}">
       <formula1>"待处理,进行中,已完成,失败,跳过"</formula1>
     </dataValidation>
   </dataValidations>

--- a/0_tasks.xlsx
+++ b/0_tasks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Nutstore\1\Thoughts\Others\20260514摄像头破解\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luessiaw\Documents\Syncthing\99_其他\20260514摄像头破解\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34DDB18-8FD8-46EB-BCA9-E30C1400861C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B9273E-7A61-43D8-8783-2557CB58F423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28130" yWindow="-21600" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8910" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1337,6 +1337,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1354,15 +1363,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1720,10 +1720,10 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1746,8 +1746,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1768,8 +1768,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="15"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1790,8 +1790,8 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1812,8 +1812,8 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="15"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1834,8 +1834,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="8" t="s">
         <v>87</v>
       </c>
@@ -1856,10 +1856,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1882,8 +1882,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="15"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1904,8 +1904,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="15"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1926,8 +1926,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="15"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1948,8 +1948,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="15"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1970,8 +1970,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="15"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +1992,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="8" t="s">
         <v>107</v>
       </c>
@@ -2014,10 +2014,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -2040,8 +2040,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="1" t="s">
         <v>28</v>
       </c>
@@ -2062,8 +2062,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
@@ -2084,8 +2084,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="1" t="s">
         <v>30</v>
       </c>
@@ -2106,8 +2106,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
@@ -2128,8 +2128,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
@@ -2150,8 +2150,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="16"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="8" t="s">
         <v>126</v>
       </c>
@@ -2172,10 +2172,10 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="17" t="s">
         <v>131</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -2198,8 +2198,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="15"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1" t="s">
         <v>35</v>
       </c>
@@ -2220,8 +2220,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="15"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="1" t="s">
         <v>36</v>
       </c>
@@ -2242,8 +2242,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="15"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="1" t="s">
         <v>37</v>
       </c>
@@ -2264,8 +2264,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="15"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
@@ -2286,8 +2286,8 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="15"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1" t="s">
         <v>39</v>
       </c>
@@ -2308,8 +2308,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
-      <c r="B28" s="15"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1" t="s">
         <v>136</v>
       </c>
@@ -2330,8 +2330,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="15"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1" t="s">
         <v>138</v>
       </c>
@@ -2352,12 +2352,12 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="15"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="11" t="s">
         <v>325</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2374,8 +2374,8 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="15"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1" t="s">
         <v>141</v>
       </c>
@@ -2396,8 +2396,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="15"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1" t="s">
         <v>303</v>
       </c>
@@ -2418,30 +2418,30 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="18" t="s">
+      <c r="A33" s="15"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F33" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G33" s="18" t="s">
+      <c r="F33" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="13" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="16"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="8" t="s">
         <v>326</v>
       </c>
@@ -2462,10 +2462,10 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="17" t="s">
         <v>142</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -2488,8 +2488,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="15"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="18"/>
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
@@ -2510,8 +2510,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="15"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="18"/>
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
@@ -2532,8 +2532,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="15"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="18"/>
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,8 +2554,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="15"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="18"/>
       <c r="C39" s="1" t="s">
         <v>44</v>
       </c>
@@ -2576,8 +2576,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="15"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="18"/>
       <c r="C40" s="1" t="s">
         <v>45</v>
       </c>
@@ -2598,8 +2598,8 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="15"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="18"/>
       <c r="C41" s="1" t="s">
         <v>46</v>
       </c>
@@ -2620,8 +2620,8 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="15"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="18"/>
       <c r="C42" s="1" t="s">
         <v>47</v>
       </c>
@@ -2642,8 +2642,8 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="15"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="18"/>
       <c r="C43" s="1" t="s">
         <v>167</v>
       </c>
@@ -2664,8 +2664,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="15"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="18"/>
       <c r="C44" s="1" t="s">
         <v>171</v>
       </c>
@@ -2686,8 +2686,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="15"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="18"/>
       <c r="C45" s="1" t="s">
         <v>175</v>
       </c>
@@ -2708,8 +2708,8 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="16"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="19"/>
       <c r="C46" s="8" t="s">
         <v>179</v>
       </c>
@@ -2730,10 +2730,10 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="17" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="5" t="s">
@@ -2756,8 +2756,8 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="15"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="18"/>
       <c r="C48" s="1" t="s">
         <v>51</v>
       </c>
@@ -2778,8 +2778,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="15"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="18"/>
       <c r="C49" s="1" t="s">
         <v>52</v>
       </c>
@@ -2800,8 +2800,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="15"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="18"/>
       <c r="C50" s="1" t="s">
         <v>53</v>
       </c>
@@ -2822,8 +2822,8 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
-      <c r="B51" s="15"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="18"/>
       <c r="C51" s="1" t="s">
         <v>55</v>
       </c>
@@ -2844,8 +2844,8 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="15"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="18"/>
       <c r="C52" s="1" t="s">
         <v>56</v>
       </c>
@@ -2866,8 +2866,8 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="15"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="18"/>
       <c r="C53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2888,8 +2888,8 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="15"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="18"/>
       <c r="C54" s="1" t="s">
         <v>205</v>
       </c>
@@ -2910,8 +2910,8 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="16"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="8" t="s">
         <v>210</v>
       </c>
@@ -2932,10 +2932,10 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="17" t="s">
         <v>214</v>
       </c>
       <c r="C56" s="5" t="s">
@@ -2958,8 +2958,8 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
-      <c r="B57" s="15"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="18"/>
       <c r="C57" s="1" t="s">
         <v>61</v>
       </c>
@@ -2980,8 +2980,8 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="15"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="18"/>
       <c r="C58" s="1" t="s">
         <v>62</v>
       </c>
@@ -3002,8 +3002,8 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="15"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="18"/>
       <c r="C59" s="1" t="s">
         <v>63</v>
       </c>
@@ -3024,8 +3024,8 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="15"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="18"/>
       <c r="C60" s="1" t="s">
         <v>65</v>
       </c>
@@ -3046,8 +3046,8 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="15"/>
+      <c r="A61" s="15"/>
+      <c r="B61" s="18"/>
       <c r="C61" s="1" t="s">
         <v>67</v>
       </c>
@@ -3068,8 +3068,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="15"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="18"/>
       <c r="C62" s="1" t="s">
         <v>68</v>
       </c>
@@ -3090,8 +3090,8 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="15"/>
+      <c r="A63" s="15"/>
+      <c r="B63" s="18"/>
       <c r="C63" s="1" t="s">
         <v>236</v>
       </c>
@@ -3112,8 +3112,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
-      <c r="B64" s="15"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="18"/>
       <c r="C64" s="1" t="s">
         <v>240</v>
       </c>
@@ -3134,8 +3134,8 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="16"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="19"/>
       <c r="C65" s="8" t="s">
         <v>245</v>
       </c>
@@ -3156,10 +3156,10 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="17" t="s">
         <v>59</v>
       </c>
       <c r="C66" s="5" t="s">
@@ -3182,8 +3182,8 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="12"/>
-      <c r="B67" s="15"/>
+      <c r="A67" s="15"/>
+      <c r="B67" s="18"/>
       <c r="C67" s="1" t="s">
         <v>254</v>
       </c>
@@ -3204,8 +3204,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="12"/>
-      <c r="B68" s="15"/>
+      <c r="A68" s="15"/>
+      <c r="B68" s="18"/>
       <c r="C68" s="1" t="s">
         <v>258</v>
       </c>
@@ -3226,8 +3226,8 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
-      <c r="B69" s="15"/>
+      <c r="A69" s="15"/>
+      <c r="B69" s="18"/>
       <c r="C69" s="1" t="s">
         <v>262</v>
       </c>
@@ -3248,8 +3248,8 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="12"/>
-      <c r="B70" s="15"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="18"/>
       <c r="C70" s="1" t="s">
         <v>267</v>
       </c>
@@ -3270,8 +3270,8 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
-      <c r="B71" s="15"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="18"/>
       <c r="C71" s="1" t="s">
         <v>270</v>
       </c>
@@ -3292,8 +3292,8 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="12"/>
-      <c r="B72" s="15"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="18"/>
       <c r="C72" s="1" t="s">
         <v>274</v>
       </c>
@@ -3314,8 +3314,8 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="12"/>
-      <c r="B73" s="15"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="18"/>
       <c r="C73" s="1" t="s">
         <v>278</v>
       </c>
@@ -3336,8 +3336,8 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="12"/>
-      <c r="B74" s="15"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="18"/>
       <c r="C74" s="1" t="s">
         <v>282</v>
       </c>
@@ -3358,8 +3358,8 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="16"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="19"/>
       <c r="C75" s="8" t="s">
         <v>285</v>
       </c>
